--- a/personal.xlsx
+++ b/personal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>id_empleado</t>
   </si>
@@ -97,7 +97,22 @@
     <t>DAVID ALEJANDRO HERNANDEZ RODRIGUEZ</t>
   </si>
   <si>
-    <t>⚪ Sin Asignar</t>
+    <t>✂️ Corte Laser</t>
+  </si>
+  <si>
+    <t>👑 Dirección</t>
+  </si>
+  <si>
+    <t>📐 Doblez</t>
+  </si>
+  <si>
+    <t>⚙️ Ingeniería</t>
+  </si>
+  <si>
+    <t>📦 Embarque</t>
+  </si>
+  <si>
+    <t>🎨 Pintura</t>
   </si>
 </sst>
 </file>
@@ -473,7 +488,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -484,7 +499,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -506,7 +521,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -517,7 +532,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -528,7 +543,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -539,7 +554,7 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -550,7 +565,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -572,7 +587,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/personal.xlsx
+++ b/personal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>id_empleado</t>
   </si>
@@ -61,6 +61,9 @@
     <t>1477</t>
   </si>
   <si>
+    <t>1145</t>
+  </si>
+  <si>
     <t>BRYAN ALEJANDRO FLORES MANCINAS</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>DAVID ALEJANDRO HERNANDEZ RODRIGUEZ</t>
   </si>
   <si>
+    <t>ARMANDO WOO VAZQUEZ</t>
+  </si>
+  <si>
     <t>✂️ Corte Laser</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
   </si>
   <si>
     <t>🎨 Pintura</t>
+  </si>
+  <si>
+    <t>⚪ Sin Asignar</t>
   </si>
 </sst>
 </file>
@@ -444,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -463,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -474,10 +483,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -485,10 +494,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -496,10 +505,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -507,10 +516,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -518,10 +527,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -529,10 +538,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -540,10 +549,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -551,10 +560,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -562,10 +571,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -573,10 +582,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -584,10 +593,21 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
